--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_20_34.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_20_34.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1222687.010167543</v>
+        <v>1227110.912842222</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5402149.821848597</v>
+        <v>5413711.842050619</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11190521.09865133</v>
+        <v>11192483.67277902</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6838051.655649283</v>
+        <v>6836117.846540689</v>
       </c>
     </row>
     <row r="11">
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2134,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8807999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2162,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8807999999999996</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2241,10 +2241,10 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8807999999999999</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2353,13 +2353,13 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8807999999999995</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2435,13 +2435,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8807999999999995</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>0</v>
@@ -2469,16 +2469,16 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8807999999999999</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2551,16 +2551,16 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8807999999999995</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -2630,13 +2630,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8807999999999996</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2757,19 +2757,19 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0.8807999999999999</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2839,13 +2839,13 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0.8807999999999999</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2867,10 +2867,10 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8115876066161209</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.06921239338387863</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -2921,13 +2921,13 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2994,16 +2994,16 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.8807999999999996</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3079,13 +3079,13 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0.8807999999999995</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3107,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.06921239338385023</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -3146,19 +3146,19 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0.8115876066161172</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3180,10 +3180,10 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8807999999999996</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -3265,13 +3265,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8807999999999996</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3319,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8807999999999996</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -3386,10 +3386,10 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -3401,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3459,10 +3459,10 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3471,10 +3471,10 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.8807999999999996</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8807999999999999</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -3502,13 +3502,13 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8115876066161209</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.06921239338387863</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3623,16 +3623,16 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -3702,22 +3702,22 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.8807999999999999</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -3742,10 +3742,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8807999999999995</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3775,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -3812,16 +3812,16 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5372828367893648</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3435171632106346</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -3857,7 +3857,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -3888,7 +3888,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -3900,10 +3900,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0.8807999999999999</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1499115084685643</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1499115084685681</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1499115084685681</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1499115084685681</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1499115084685681</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.170113528670588</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.160012518569578</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.160012518569578</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.1499115084685681</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0.1499115084685681</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.1499115084685681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1499115084685643</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1499115084685643</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1499115084685643</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>1.979797979797979</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9696969696969693</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4269870335460956</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.98989898989899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>2.10020202020202</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1.09010101010101</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>3.11030303030303</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>221.0494470045765</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L20" t="n">
         <v>235.7664149699872</v>
@@ -9390,13 +9390,13 @@
         <v>230.3462332272727</v>
       </c>
       <c r="N20" t="n">
-        <v>230.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O20" t="n">
-        <v>231.0982114216867</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P20" t="n">
-        <v>232.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q20" t="n">
         <v>212.3149906599047</v>
@@ -9460,7 +9460,7 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>138.801034933955</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
         <v>138.5543797798742</v>
@@ -9469,13 +9469,13 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N21" t="n">
-        <v>132.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O21" t="n">
-        <v>143.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P21" t="n">
-        <v>134.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
         <v>139.9817740860215</v>
@@ -9542,16 +9542,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L22" t="n">
-        <v>135.8442722408342</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M22" t="n">
-        <v>139.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N22" t="n">
-        <v>128.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O22" t="n">
-        <v>139.4565384518428</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P22" t="n">
         <v>135.0065633140411</v>
@@ -9621,16 +9621,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L23" t="n">
-        <v>236.7260109295832</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M23" t="n">
-        <v>231.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N23" t="n">
-        <v>230.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O23" t="n">
-        <v>231.0982114216867</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P23" t="n">
         <v>231.2329957552695</v>
@@ -9700,16 +9700,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>139.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M24" t="n">
-        <v>143.0936298816143</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
-        <v>132.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O24" t="n">
-        <v>143.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P24" t="n">
         <v>133.9744074143302</v>
@@ -9779,16 +9779,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L25" t="n">
-        <v>135.8442722408342</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M25" t="n">
-        <v>139.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N25" t="n">
-        <v>128.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O25" t="n">
-        <v>139.4565384518428</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P25" t="n">
         <v>135.0065633140411</v>
@@ -9855,16 +9855,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>221.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L26" t="n">
-        <v>236.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M26" t="n">
-        <v>231.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N26" t="n">
-        <v>230.3726595561869</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O26" t="n">
         <v>230.0982114216867</v>
@@ -9940,16 +9940,16 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
-        <v>143.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N27" t="n">
-        <v>132.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>143.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>134.9340033739262</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
         <v>139.9817740860215</v>
@@ -10016,16 +10016,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L28" t="n">
-        <v>135.8442722408342</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M28" t="n">
-        <v>139.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N28" t="n">
-        <v>128.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O28" t="n">
-        <v>139.4565384518428</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P28" t="n">
         <v>135.0065633140411</v>
@@ -10095,19 +10095,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L29" t="n">
-        <v>236.7260109295832</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M29" t="n">
-        <v>231.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N29" t="n">
-        <v>230.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O29" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P29" t="n">
-        <v>232.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10174,22 +10174,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>139.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
-        <v>143.0936298816143</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>143.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P30" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
-        <v>140.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10253,16 +10253,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L31" t="n">
-        <v>135.8442722408342</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M31" t="n">
-        <v>139.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N31" t="n">
-        <v>128.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O31" t="n">
-        <v>139.4565384518428</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P31" t="n">
         <v>135.0065633140411</v>
@@ -10332,19 +10332,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L32" t="n">
-        <v>236.7260109295832</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M32" t="n">
-        <v>231.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N32" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O32" t="n">
-        <v>231.0982114216867</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P32" t="n">
-        <v>232.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10408,16 +10408,16 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>138.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>139.5139757394701</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>143.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N33" t="n">
-        <v>132.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
         <v>142.5962444444444</v>
@@ -10490,16 +10490,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L34" t="n">
-        <v>135.8442722408342</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M34" t="n">
-        <v>139.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N34" t="n">
-        <v>128.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O34" t="n">
-        <v>139.4565384518428</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P34" t="n">
         <v>135.0065633140411</v>
@@ -10566,16 +10566,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>221.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L35" t="n">
-        <v>236.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M35" t="n">
-        <v>231.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N35" t="n">
-        <v>230.3726595561869</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O35" t="n">
         <v>230.0982114216867</v>
@@ -10645,7 +10645,7 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>138.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
         <v>138.5543797798742</v>
@@ -10654,13 +10654,13 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N36" t="n">
-        <v>132.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>143.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>134.9340033739262</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
         <v>139.9817740860215</v>
@@ -10727,16 +10727,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L37" t="n">
-        <v>135.8442722408342</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M37" t="n">
-        <v>139.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N37" t="n">
-        <v>128.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O37" t="n">
-        <v>139.4565384518428</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P37" t="n">
         <v>135.0065633140411</v>
@@ -10809,16 +10809,16 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M38" t="n">
-        <v>231.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N38" t="n">
-        <v>230.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O38" t="n">
-        <v>231.0982114216867</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P38" t="n">
-        <v>232.1925917148655</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q38" t="n">
         <v>212.3149906599047</v>
@@ -10885,19 +10885,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>139.5139757394701</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M39" t="n">
-        <v>143.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>132.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>134.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
         <v>139.9817740860215</v>
@@ -10964,16 +10964,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L40" t="n">
-        <v>135.8442722408342</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M40" t="n">
-        <v>139.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N40" t="n">
-        <v>128.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O40" t="n">
-        <v>139.4565384518428</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P40" t="n">
         <v>135.0065633140411</v>
@@ -11040,16 +11040,16 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>221.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L41" t="n">
-        <v>236.7664149699872</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M41" t="n">
-        <v>231.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N41" t="n">
-        <v>230.3726595561869</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O41" t="n">
         <v>230.0982114216867</v>
@@ -11122,19 +11122,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>139.5139757394701</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
-        <v>143.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
-        <v>132.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>134.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q42" t="n">
         <v>139.9817740860215</v>
@@ -11201,16 +11201,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L43" t="n">
-        <v>135.8442722408342</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M43" t="n">
-        <v>139.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N43" t="n">
-        <v>128.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O43" t="n">
-        <v>139.4565384518428</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P43" t="n">
         <v>135.0065633140411</v>
@@ -23215,28 +23215,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>370.7338416634806</v>
+        <v>370.7845523088681</v>
       </c>
       <c r="C11" t="n">
-        <v>353.2728917710076</v>
+        <v>353.323602416395</v>
       </c>
       <c r="D11" t="n">
-        <v>342.683041620683</v>
+        <v>342.7337522660704</v>
       </c>
       <c r="E11" t="n">
-        <v>369.9303700722618</v>
+        <v>369.9810807176493</v>
       </c>
       <c r="F11" t="n">
-        <v>394.8760457417114</v>
+        <v>394.9267563870989</v>
       </c>
       <c r="G11" t="n">
-        <v>403.302737515135</v>
+        <v>403.3534481605225</v>
       </c>
       <c r="H11" t="n">
-        <v>327.4748021157671</v>
+        <v>327.5255127611546</v>
       </c>
       <c r="I11" t="n">
-        <v>198.4758895704059</v>
+        <v>198.5266002157934</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -23263,28 +23263,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>137.8691179411497</v>
+        <v>137.9198285865372</v>
       </c>
       <c r="S11" t="n">
-        <v>197.0200695862453</v>
+        <v>197.0707802316328</v>
       </c>
       <c r="T11" t="n">
-        <v>211.0958495641314</v>
+        <v>211.1465602095188</v>
       </c>
       <c r="U11" t="n">
-        <v>239.3456529078365</v>
+        <v>239.396363553224</v>
       </c>
       <c r="V11" t="n">
-        <v>315.7522584701349</v>
+        <v>315.8029691155224</v>
       </c>
       <c r="W11" t="n">
-        <v>337.240968717413</v>
+        <v>337.2916793628005</v>
       </c>
       <c r="X11" t="n">
-        <v>357.731100678469</v>
+        <v>357.7818113238565</v>
       </c>
       <c r="Y11" t="n">
-        <v>374.2379386560536</v>
+        <v>374.2886493014411</v>
       </c>
     </row>
     <row r="12">
@@ -23294,28 +23294,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>154.5331836498673</v>
+        <v>154.5838942952548</v>
       </c>
       <c r="C12" t="n">
-        <v>160.7084989883157</v>
+        <v>160.7592096337032</v>
       </c>
       <c r="D12" t="n">
-        <v>135.4450655646388</v>
+        <v>135.4957762100262</v>
       </c>
       <c r="E12" t="n">
-        <v>145.6450804554009</v>
+        <v>145.6957911007884</v>
       </c>
       <c r="F12" t="n">
-        <v>133.0692123933839</v>
+        <v>133.1199230387714</v>
       </c>
       <c r="G12" t="n">
-        <v>125.3435171632106</v>
+        <v>125.3942278085981</v>
       </c>
       <c r="H12" t="n">
-        <v>100.2354442364965</v>
+        <v>100.2861548818839</v>
       </c>
       <c r="I12" t="n">
-        <v>77.39663285141508</v>
+        <v>77.44734349680256</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>88.15783415264313</v>
+        <v>88.20854479803062</v>
       </c>
       <c r="S12" t="n">
-        <v>159.6831711038378</v>
+        <v>159.7338817492253</v>
       </c>
       <c r="T12" t="n">
-        <v>188.1647286948216</v>
+        <v>188.2154393402091</v>
       </c>
       <c r="U12" t="n">
-        <v>213.9413820809748</v>
+        <v>213.9920927263623</v>
       </c>
       <c r="V12" t="n">
-        <v>220.8005871494253</v>
+        <v>220.8512977948128</v>
       </c>
       <c r="W12" t="n">
-        <v>239.6949831609196</v>
+        <v>239.7456938063071</v>
       </c>
       <c r="X12" t="n">
-        <v>193.7729852034775</v>
+        <v>193.823695848865</v>
       </c>
       <c r="Y12" t="n">
-        <v>193.6826957773044</v>
+        <v>193.7334064226918</v>
       </c>
     </row>
     <row r="13">
@@ -23373,34 +23373,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>167.8319801819373</v>
+        <v>167.8826908273248</v>
       </c>
       <c r="C13" t="n">
-        <v>155.2468210986278</v>
+        <v>155.2975317440153</v>
       </c>
       <c r="D13" t="n">
-        <v>136.6154730182124</v>
+        <v>136.6661836635998</v>
       </c>
       <c r="E13" t="n">
-        <v>134.4339626465692</v>
+        <v>134.4846732919567</v>
       </c>
       <c r="F13" t="n">
-        <v>133.4210480229312</v>
+        <v>133.4717586683187</v>
       </c>
       <c r="G13" t="n">
-        <v>155.9909793584588</v>
+        <v>156.0416900038462</v>
       </c>
       <c r="H13" t="n">
-        <v>150.2271725074396</v>
+        <v>150.2778831528271</v>
       </c>
       <c r="I13" t="n">
-        <v>143.4504749272583</v>
+        <v>143.5011855726458</v>
       </c>
       <c r="J13" t="n">
-        <v>81.35918011667277</v>
+        <v>81.40989076206026</v>
       </c>
       <c r="K13" t="n">
-        <v>10.26949182588285</v>
+        <v>10.32020247127033</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,31 +23418,31 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>74.16204325169439</v>
+        <v>74.21275389708187</v>
       </c>
       <c r="R13" t="n">
-        <v>165.2933913771695</v>
+        <v>165.344102022557</v>
       </c>
       <c r="S13" t="n">
-        <v>212.0165980369723</v>
+        <v>212.0673086823597</v>
       </c>
       <c r="T13" t="n">
-        <v>215.9455894282815</v>
+        <v>215.996300073669</v>
       </c>
       <c r="U13" t="n">
-        <v>274.3190293564909</v>
+        <v>274.3697400018784</v>
       </c>
       <c r="V13" t="n">
-        <v>240.137643323828</v>
+        <v>240.1883539692155</v>
       </c>
       <c r="W13" t="n">
-        <v>274.522998336591</v>
+        <v>274.5737089819785</v>
       </c>
       <c r="X13" t="n">
-        <v>213.7096553890372</v>
+        <v>213.7603660344246</v>
       </c>
       <c r="Y13" t="n">
-        <v>206.5846533520948</v>
+        <v>206.6353639974823</v>
       </c>
     </row>
     <row r="14">
@@ -23452,28 +23452,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>291.7338416634806</v>
+        <v>291.4725427837783</v>
       </c>
       <c r="C14" t="n">
-        <v>274.2728917710076</v>
+        <v>274.0115928913053</v>
       </c>
       <c r="D14" t="n">
-        <v>263.683041620683</v>
+        <v>263.4217427409807</v>
       </c>
       <c r="E14" t="n">
-        <v>290.9303700722618</v>
+        <v>290.6690711925595</v>
       </c>
       <c r="F14" t="n">
-        <v>315.8760457417114</v>
+        <v>315.6147468620092</v>
       </c>
       <c r="G14" t="n">
-        <v>324.302737515135</v>
+        <v>324.0414386354328</v>
       </c>
       <c r="H14" t="n">
-        <v>248.4748021157671</v>
+        <v>248.2135032360649</v>
       </c>
       <c r="I14" t="n">
-        <v>119.4758895704059</v>
+        <v>119.2145906907037</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23500,28 +23500,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>58.86911794114968</v>
+        <v>58.60781906144743</v>
       </c>
       <c r="S14" t="n">
-        <v>118.0200695862453</v>
+        <v>117.7587707065431</v>
       </c>
       <c r="T14" t="n">
-        <v>132.0958495641314</v>
+        <v>131.8345506844291</v>
       </c>
       <c r="U14" t="n">
-        <v>160.3456529078365</v>
+        <v>160.0843540281342</v>
       </c>
       <c r="V14" t="n">
-        <v>236.7522584701349</v>
+        <v>236.4909595904327</v>
       </c>
       <c r="W14" t="n">
-        <v>258.240968717413</v>
+        <v>257.9796698377107</v>
       </c>
       <c r="X14" t="n">
-        <v>278.731100678469</v>
+        <v>278.4698017987668</v>
       </c>
       <c r="Y14" t="n">
-        <v>295.2379386560536</v>
+        <v>294.9766397763514</v>
       </c>
     </row>
     <row r="15">
@@ -23531,25 +23531,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75.53318364986734</v>
+        <v>75.27188477016509</v>
       </c>
       <c r="C15" t="n">
-        <v>81.70849898831574</v>
+        <v>81.44720010861349</v>
       </c>
       <c r="D15" t="n">
-        <v>56.44506556463875</v>
+        <v>56.1837666849365</v>
       </c>
       <c r="E15" t="n">
-        <v>66.64508045540094</v>
+        <v>66.38378157569869</v>
       </c>
       <c r="F15" t="n">
-        <v>54.06921239338388</v>
+        <v>53.80791351368163</v>
       </c>
       <c r="G15" t="n">
-        <v>46.34351716321063</v>
+        <v>46.08221828350838</v>
       </c>
       <c r="H15" t="n">
-        <v>21.23544423649646</v>
+        <v>20.97414535679421</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23579,28 +23579,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>9.157834152643133</v>
+        <v>8.896535272940881</v>
       </c>
       <c r="S15" t="n">
-        <v>80.68317110383782</v>
+        <v>80.42187222413557</v>
       </c>
       <c r="T15" t="n">
-        <v>109.1647286948216</v>
+        <v>108.9034298151194</v>
       </c>
       <c r="U15" t="n">
-        <v>134.9413820809748</v>
+        <v>134.6800832012726</v>
       </c>
       <c r="V15" t="n">
-        <v>141.8005871494253</v>
+        <v>141.539288269723</v>
       </c>
       <c r="W15" t="n">
-        <v>160.6949831609196</v>
+        <v>160.4336842812174</v>
       </c>
       <c r="X15" t="n">
-        <v>114.7729852034775</v>
+        <v>114.5116863237752</v>
       </c>
       <c r="Y15" t="n">
-        <v>114.6826957773044</v>
+        <v>114.4213968976021</v>
       </c>
     </row>
     <row r="16">
@@ -23610,31 +23610,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>88.8319801819373</v>
+        <v>88.57068130223504</v>
       </c>
       <c r="C16" t="n">
-        <v>76.24682109862783</v>
+        <v>75.98552221892558</v>
       </c>
       <c r="D16" t="n">
-        <v>57.61547301821236</v>
+        <v>57.3541741385101</v>
       </c>
       <c r="E16" t="n">
-        <v>55.43396264656917</v>
+        <v>55.17266376686692</v>
       </c>
       <c r="F16" t="n">
-        <v>54.42104802293125</v>
+        <v>54.15974914322899</v>
       </c>
       <c r="G16" t="n">
-        <v>76.99097935845876</v>
+        <v>76.72968047875651</v>
       </c>
       <c r="H16" t="n">
-        <v>71.22717250743958</v>
+        <v>70.96587362773732</v>
       </c>
       <c r="I16" t="n">
-        <v>64.45047492725828</v>
+        <v>64.18917604755603</v>
       </c>
       <c r="J16" t="n">
-        <v>2.359180116672775</v>
+        <v>2.097881236970522</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23658,28 +23658,28 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>86.29339137716948</v>
+        <v>86.03209249746723</v>
       </c>
       <c r="S16" t="n">
-        <v>133.0165980369723</v>
+        <v>132.75529915727</v>
       </c>
       <c r="T16" t="n">
-        <v>136.9455894282815</v>
+        <v>136.6842905485792</v>
       </c>
       <c r="U16" t="n">
-        <v>195.3190293564909</v>
+        <v>195.0577304767886</v>
       </c>
       <c r="V16" t="n">
-        <v>161.137643323828</v>
+        <v>160.8763444441257</v>
       </c>
       <c r="W16" t="n">
-        <v>195.522998336591</v>
+        <v>195.2616994568887</v>
       </c>
       <c r="X16" t="n">
-        <v>134.7096553890372</v>
+        <v>134.4483565093349</v>
       </c>
       <c r="Y16" t="n">
-        <v>127.5846533520948</v>
+        <v>127.3233544723925</v>
       </c>
     </row>
     <row r="17">
@@ -23689,28 +23689,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>291.7338416634806</v>
+        <v>291.4725427837783</v>
       </c>
       <c r="C17" t="n">
-        <v>274.2728917710076</v>
+        <v>274.0115928913053</v>
       </c>
       <c r="D17" t="n">
-        <v>263.683041620683</v>
+        <v>263.4217427409807</v>
       </c>
       <c r="E17" t="n">
-        <v>290.9303700722618</v>
+        <v>290.6690711925595</v>
       </c>
       <c r="F17" t="n">
-        <v>315.8760457417114</v>
+        <v>315.6147468620092</v>
       </c>
       <c r="G17" t="n">
-        <v>324.302737515135</v>
+        <v>324.0414386354328</v>
       </c>
       <c r="H17" t="n">
-        <v>248.4748021157671</v>
+        <v>248.2135032360649</v>
       </c>
       <c r="I17" t="n">
-        <v>119.4758895704059</v>
+        <v>119.2145906907037</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23737,28 +23737,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>58.86911794114968</v>
+        <v>58.60781906144743</v>
       </c>
       <c r="S17" t="n">
-        <v>118.0200695862453</v>
+        <v>117.7587707065431</v>
       </c>
       <c r="T17" t="n">
-        <v>132.0958495641314</v>
+        <v>131.8345506844291</v>
       </c>
       <c r="U17" t="n">
-        <v>160.3456529078365</v>
+        <v>160.0843540281342</v>
       </c>
       <c r="V17" t="n">
-        <v>236.7522584701349</v>
+        <v>236.4909595904327</v>
       </c>
       <c r="W17" t="n">
-        <v>258.240968717413</v>
+        <v>257.9796698377107</v>
       </c>
       <c r="X17" t="n">
-        <v>278.731100678469</v>
+        <v>278.4698017987668</v>
       </c>
       <c r="Y17" t="n">
-        <v>295.2379386560536</v>
+        <v>294.9766397763514</v>
       </c>
     </row>
     <row r="18">
@@ -23768,25 +23768,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>75.53318364986734</v>
+        <v>75.27188477016509</v>
       </c>
       <c r="C18" t="n">
-        <v>81.70849898831574</v>
+        <v>81.44720010861349</v>
       </c>
       <c r="D18" t="n">
-        <v>56.44506556463875</v>
+        <v>56.1837666849365</v>
       </c>
       <c r="E18" t="n">
-        <v>66.64508045540094</v>
+        <v>66.38378157569869</v>
       </c>
       <c r="F18" t="n">
-        <v>54.06921239338388</v>
+        <v>53.80791351368163</v>
       </c>
       <c r="G18" t="n">
-        <v>46.34351716321063</v>
+        <v>46.08221828350838</v>
       </c>
       <c r="H18" t="n">
-        <v>21.23544423649646</v>
+        <v>20.97414535679421</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -23816,28 +23816,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>9.157834152643133</v>
+        <v>8.896535272940881</v>
       </c>
       <c r="S18" t="n">
-        <v>80.68317110383782</v>
+        <v>80.42187222413557</v>
       </c>
       <c r="T18" t="n">
-        <v>109.1647286948216</v>
+        <v>108.9034298151194</v>
       </c>
       <c r="U18" t="n">
-        <v>134.9413820809748</v>
+        <v>134.6800832012726</v>
       </c>
       <c r="V18" t="n">
-        <v>141.8005871494253</v>
+        <v>141.539288269723</v>
       </c>
       <c r="W18" t="n">
-        <v>160.6949831609196</v>
+        <v>160.4336842812174</v>
       </c>
       <c r="X18" t="n">
-        <v>114.7729852034775</v>
+        <v>114.5116863237752</v>
       </c>
       <c r="Y18" t="n">
-        <v>114.6826957773044</v>
+        <v>114.4213968976021</v>
       </c>
     </row>
     <row r="19">
@@ -23847,31 +23847,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88.8319801819373</v>
+        <v>88.57068130223504</v>
       </c>
       <c r="C19" t="n">
-        <v>76.24682109862783</v>
+        <v>75.98552221892558</v>
       </c>
       <c r="D19" t="n">
-        <v>57.61547301821236</v>
+        <v>57.3541741385101</v>
       </c>
       <c r="E19" t="n">
-        <v>55.43396264656917</v>
+        <v>55.17266376686692</v>
       </c>
       <c r="F19" t="n">
-        <v>54.42104802293125</v>
+        <v>54.15974914322899</v>
       </c>
       <c r="G19" t="n">
-        <v>76.99097935845876</v>
+        <v>76.72968047875651</v>
       </c>
       <c r="H19" t="n">
-        <v>71.22717250743958</v>
+        <v>70.96587362773732</v>
       </c>
       <c r="I19" t="n">
-        <v>64.45047492725828</v>
+        <v>64.18917604755603</v>
       </c>
       <c r="J19" t="n">
-        <v>2.359180116672775</v>
+        <v>2.097881236970522</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -23895,28 +23895,28 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>86.29339137716948</v>
+        <v>86.03209249746723</v>
       </c>
       <c r="S19" t="n">
-        <v>133.0165980369723</v>
+        <v>132.75529915727</v>
       </c>
       <c r="T19" t="n">
-        <v>136.9455894282815</v>
+        <v>136.6842905485792</v>
       </c>
       <c r="U19" t="n">
-        <v>195.3190293564909</v>
+        <v>195.0577304767886</v>
       </c>
       <c r="V19" t="n">
-        <v>161.137643323828</v>
+        <v>160.8763444441257</v>
       </c>
       <c r="W19" t="n">
-        <v>195.522998336591</v>
+        <v>195.2616994568887</v>
       </c>
       <c r="X19" t="n">
-        <v>134.7096553890372</v>
+        <v>134.4483565093349</v>
       </c>
       <c r="Y19" t="n">
-        <v>127.5846533520948</v>
+        <v>127.3233544723925</v>
       </c>
     </row>
     <row r="20">
@@ -23926,28 +23926,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>291.7338416634806</v>
+        <v>291.4725427837783</v>
       </c>
       <c r="C20" t="n">
-        <v>273.2728917710076</v>
+        <v>274.0115928913053</v>
       </c>
       <c r="D20" t="n">
-        <v>263.683041620683</v>
+        <v>263.4217427409807</v>
       </c>
       <c r="E20" t="n">
-        <v>290.9303700722618</v>
+        <v>290.6690711925595</v>
       </c>
       <c r="F20" t="n">
-        <v>315.8760457417114</v>
+        <v>315.6147468620092</v>
       </c>
       <c r="G20" t="n">
-        <v>324.302737515135</v>
+        <v>324.0414386354328</v>
       </c>
       <c r="H20" t="n">
-        <v>247.4748021157671</v>
+        <v>248.2135032360649</v>
       </c>
       <c r="I20" t="n">
-        <v>119.4758895704059</v>
+        <v>119.2145906907037</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -23974,28 +23974,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>58.86911794114968</v>
+        <v>58.60781906144743</v>
       </c>
       <c r="S20" t="n">
-        <v>118.0200695862453</v>
+        <v>117.7587707065431</v>
       </c>
       <c r="T20" t="n">
-        <v>132.0958495641314</v>
+        <v>131.8345506844291</v>
       </c>
       <c r="U20" t="n">
-        <v>160.3456529078365</v>
+        <v>160.0843540281342</v>
       </c>
       <c r="V20" t="n">
-        <v>236.7522584701349</v>
+        <v>236.4909595904327</v>
       </c>
       <c r="W20" t="n">
-        <v>258.240968717413</v>
+        <v>257.9796698377107</v>
       </c>
       <c r="X20" t="n">
-        <v>277.850300678469</v>
+        <v>278.4698017987668</v>
       </c>
       <c r="Y20" t="n">
-        <v>294.2379386560536</v>
+        <v>294.9766397763514</v>
       </c>
     </row>
     <row r="21">
@@ -24005,25 +24005,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>74.53318364986734</v>
+        <v>75.27188477016509</v>
       </c>
       <c r="C21" t="n">
-        <v>80.70849898831574</v>
+        <v>81.44720010861349</v>
       </c>
       <c r="D21" t="n">
-        <v>56.44506556463875</v>
+        <v>56.1837666849365</v>
       </c>
       <c r="E21" t="n">
-        <v>66.64508045540094</v>
+        <v>66.38378157569869</v>
       </c>
       <c r="F21" t="n">
-        <v>54.06921239338388</v>
+        <v>53.80791351368163</v>
       </c>
       <c r="G21" t="n">
-        <v>45.46271716321064</v>
+        <v>46.08221828350838</v>
       </c>
       <c r="H21" t="n">
-        <v>21.23544423649646</v>
+        <v>20.97414535679421</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -24053,28 +24053,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>9.157834152643133</v>
+        <v>8.896535272940881</v>
       </c>
       <c r="S21" t="n">
-        <v>80.68317110383782</v>
+        <v>80.42187222413557</v>
       </c>
       <c r="T21" t="n">
-        <v>109.1647286948216</v>
+        <v>108.9034298151194</v>
       </c>
       <c r="U21" t="n">
-        <v>134.9413820809748</v>
+        <v>134.6800832012726</v>
       </c>
       <c r="V21" t="n">
-        <v>141.8005871494253</v>
+        <v>141.539288269723</v>
       </c>
       <c r="W21" t="n">
-        <v>160.6949831609196</v>
+        <v>160.4336842812174</v>
       </c>
       <c r="X21" t="n">
-        <v>114.7729852034775</v>
+        <v>114.5116863237752</v>
       </c>
       <c r="Y21" t="n">
-        <v>113.6826957773044</v>
+        <v>114.4213968976021</v>
       </c>
     </row>
     <row r="22">
@@ -24084,31 +24084,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>87.8319801819373</v>
+        <v>88.57068130223504</v>
       </c>
       <c r="C22" t="n">
-        <v>76.24682109862783</v>
+        <v>75.98552221892558</v>
       </c>
       <c r="D22" t="n">
-        <v>57.61547301821236</v>
+        <v>57.3541741385101</v>
       </c>
       <c r="E22" t="n">
-        <v>55.43396264656917</v>
+        <v>55.17266376686692</v>
       </c>
       <c r="F22" t="n">
-        <v>54.42104802293125</v>
+        <v>54.15974914322899</v>
       </c>
       <c r="G22" t="n">
-        <v>75.99097935845876</v>
+        <v>76.72968047875651</v>
       </c>
       <c r="H22" t="n">
-        <v>70.22717250743958</v>
+        <v>70.96587362773732</v>
       </c>
       <c r="I22" t="n">
-        <v>64.45047492725828</v>
+        <v>64.18917604755603</v>
       </c>
       <c r="J22" t="n">
-        <v>2.359180116672775</v>
+        <v>2.097881236970522</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -24132,28 +24132,28 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>86.29339137716948</v>
+        <v>86.03209249746723</v>
       </c>
       <c r="S22" t="n">
-        <v>132.1357980369723</v>
+        <v>132.75529915727</v>
       </c>
       <c r="T22" t="n">
-        <v>136.9455894282815</v>
+        <v>136.6842905485792</v>
       </c>
       <c r="U22" t="n">
-        <v>195.3190293564909</v>
+        <v>195.0577304767886</v>
       </c>
       <c r="V22" t="n">
-        <v>161.137643323828</v>
+        <v>160.8763444441257</v>
       </c>
       <c r="W22" t="n">
-        <v>195.522998336591</v>
+        <v>195.2616994568887</v>
       </c>
       <c r="X22" t="n">
-        <v>134.7096553890372</v>
+        <v>134.4483565093349</v>
       </c>
       <c r="Y22" t="n">
-        <v>127.5846533520948</v>
+        <v>127.3233544723925</v>
       </c>
     </row>
     <row r="23">
@@ -24163,28 +24163,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>290.7338416634806</v>
+        <v>291.4725427837783</v>
       </c>
       <c r="C23" t="n">
-        <v>274.2728917710076</v>
+        <v>274.0115928913053</v>
       </c>
       <c r="D23" t="n">
-        <v>263.683041620683</v>
+        <v>263.4217427409807</v>
       </c>
       <c r="E23" t="n">
-        <v>290.9303700722618</v>
+        <v>290.6690711925595</v>
       </c>
       <c r="F23" t="n">
-        <v>315.8760457417114</v>
+        <v>315.6147468620092</v>
       </c>
       <c r="G23" t="n">
-        <v>323.302737515135</v>
+        <v>324.0414386354328</v>
       </c>
       <c r="H23" t="n">
-        <v>248.4748021157671</v>
+        <v>248.2135032360649</v>
       </c>
       <c r="I23" t="n">
-        <v>119.4758895704059</v>
+        <v>119.2145906907037</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -24211,28 +24211,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>57.86911794114968</v>
+        <v>58.60781906144743</v>
       </c>
       <c r="S23" t="n">
-        <v>118.0200695862453</v>
+        <v>117.7587707065431</v>
       </c>
       <c r="T23" t="n">
-        <v>131.2150495641314</v>
+        <v>131.8345506844291</v>
       </c>
       <c r="U23" t="n">
-        <v>160.3456529078365</v>
+        <v>160.0843540281342</v>
       </c>
       <c r="V23" t="n">
-        <v>236.7522584701349</v>
+        <v>236.4909595904327</v>
       </c>
       <c r="W23" t="n">
-        <v>258.240968717413</v>
+        <v>257.9796698377107</v>
       </c>
       <c r="X23" t="n">
-        <v>278.731100678469</v>
+        <v>278.4698017987668</v>
       </c>
       <c r="Y23" t="n">
-        <v>295.2379386560536</v>
+        <v>294.9766397763514</v>
       </c>
     </row>
     <row r="24">
@@ -24242,25 +24242,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>75.53318364986734</v>
+        <v>75.27188477016509</v>
       </c>
       <c r="C24" t="n">
-        <v>81.70849898831574</v>
+        <v>81.44720010861349</v>
       </c>
       <c r="D24" t="n">
-        <v>56.44506556463875</v>
+        <v>56.1837666849365</v>
       </c>
       <c r="E24" t="n">
-        <v>66.64508045540094</v>
+        <v>66.38378157569869</v>
       </c>
       <c r="F24" t="n">
-        <v>54.06921239338388</v>
+        <v>53.80791351368163</v>
       </c>
       <c r="G24" t="n">
-        <v>46.34351716321063</v>
+        <v>46.08221828350838</v>
       </c>
       <c r="H24" t="n">
-        <v>21.23544423649646</v>
+        <v>20.97414535679421</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -24290,28 +24290,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>9.157834152643133</v>
+        <v>8.896535272940881</v>
       </c>
       <c r="S24" t="n">
-        <v>79.68317110383782</v>
+        <v>80.42187222413557</v>
       </c>
       <c r="T24" t="n">
-        <v>108.2839286948216</v>
+        <v>108.9034298151194</v>
       </c>
       <c r="U24" t="n">
-        <v>133.9413820809748</v>
+        <v>134.6800832012726</v>
       </c>
       <c r="V24" t="n">
-        <v>141.8005871494253</v>
+        <v>141.539288269723</v>
       </c>
       <c r="W24" t="n">
-        <v>160.6949831609196</v>
+        <v>160.4336842812174</v>
       </c>
       <c r="X24" t="n">
-        <v>113.7729852034775</v>
+        <v>114.5116863237752</v>
       </c>
       <c r="Y24" t="n">
-        <v>114.6826957773044</v>
+        <v>114.4213968976021</v>
       </c>
     </row>
     <row r="25">
@@ -24321,31 +24321,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>88.8319801819373</v>
+        <v>88.57068130223504</v>
       </c>
       <c r="C25" t="n">
-        <v>76.24682109862783</v>
+        <v>75.98552221892558</v>
       </c>
       <c r="D25" t="n">
-        <v>56.73467301821236</v>
+        <v>57.3541741385101</v>
       </c>
       <c r="E25" t="n">
-        <v>54.43396264656917</v>
+        <v>55.17266376686692</v>
       </c>
       <c r="F25" t="n">
-        <v>53.42104802293125</v>
+        <v>54.15974914322899</v>
       </c>
       <c r="G25" t="n">
-        <v>75.99097935845876</v>
+        <v>76.72968047875651</v>
       </c>
       <c r="H25" t="n">
-        <v>71.22717250743958</v>
+        <v>70.96587362773732</v>
       </c>
       <c r="I25" t="n">
-        <v>64.45047492725828</v>
+        <v>64.18917604755603</v>
       </c>
       <c r="J25" t="n">
-        <v>2.359180116672775</v>
+        <v>2.097881236970522</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -24369,28 +24369,28 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>86.29339137716948</v>
+        <v>86.03209249746723</v>
       </c>
       <c r="S25" t="n">
-        <v>133.0165980369723</v>
+        <v>132.75529915727</v>
       </c>
       <c r="T25" t="n">
-        <v>136.9455894282815</v>
+        <v>136.6842905485792</v>
       </c>
       <c r="U25" t="n">
-        <v>195.3190293564909</v>
+        <v>195.0577304767886</v>
       </c>
       <c r="V25" t="n">
-        <v>161.137643323828</v>
+        <v>160.8763444441257</v>
       </c>
       <c r="W25" t="n">
-        <v>195.522998336591</v>
+        <v>195.2616994568887</v>
       </c>
       <c r="X25" t="n">
-        <v>134.7096553890372</v>
+        <v>134.4483565093349</v>
       </c>
       <c r="Y25" t="n">
-        <v>127.5846533520948</v>
+        <v>127.3233544723925</v>
       </c>
     </row>
     <row r="26">
@@ -24400,28 +24400,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>295.7338416634806</v>
+        <v>295.6961369082176</v>
       </c>
       <c r="C26" t="n">
-        <v>278.2728917710076</v>
+        <v>278.2351870157446</v>
       </c>
       <c r="D26" t="n">
-        <v>267.683041620683</v>
+        <v>267.6453368654199</v>
       </c>
       <c r="E26" t="n">
-        <v>293.9303700722618</v>
+        <v>294.8926653169988</v>
       </c>
       <c r="F26" t="n">
-        <v>318.8760457417114</v>
+        <v>319.8383409864484</v>
       </c>
       <c r="G26" t="n">
-        <v>327.421937515135</v>
+        <v>328.265032759872</v>
       </c>
       <c r="H26" t="n">
-        <v>251.4748021157671</v>
+        <v>252.4370973605042</v>
       </c>
       <c r="I26" t="n">
-        <v>123.4758895704059</v>
+        <v>123.4381848151429</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -24448,28 +24448,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>62.86911794114968</v>
+        <v>62.8314131858867</v>
       </c>
       <c r="S26" t="n">
-        <v>122.0200695862453</v>
+        <v>121.9823648309824</v>
       </c>
       <c r="T26" t="n">
-        <v>136.0958495641314</v>
+        <v>136.0581448088684</v>
       </c>
       <c r="U26" t="n">
-        <v>164.3456529078365</v>
+        <v>164.3079481525735</v>
       </c>
       <c r="V26" t="n">
-        <v>240.7522584701349</v>
+        <v>240.7145537148719</v>
       </c>
       <c r="W26" t="n">
-        <v>262.240968717413</v>
+        <v>262.20326396215</v>
       </c>
       <c r="X26" t="n">
-        <v>282.731100678469</v>
+        <v>282.693395923206</v>
       </c>
       <c r="Y26" t="n">
-        <v>299.2379386560536</v>
+        <v>299.2002339007906</v>
       </c>
     </row>
     <row r="27">
@@ -24479,28 +24479,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>78.53318364986734</v>
+        <v>79.49547889460436</v>
       </c>
       <c r="C27" t="n">
-        <v>85.70849898831574</v>
+        <v>85.67079423305276</v>
       </c>
       <c r="D27" t="n">
-        <v>60.44506556463875</v>
+        <v>60.40736080937577</v>
       </c>
       <c r="E27" t="n">
-        <v>69.64508045540094</v>
+        <v>70.60737570013796</v>
       </c>
       <c r="F27" t="n">
-        <v>58.06921239338388</v>
+        <v>58.0315076381209</v>
       </c>
       <c r="G27" t="n">
-        <v>49.46271716321064</v>
+        <v>50.30581240794766</v>
       </c>
       <c r="H27" t="n">
-        <v>25.23544423649646</v>
+        <v>25.19773948123348</v>
       </c>
       <c r="I27" t="n">
-        <v>2.396632851415077</v>
+        <v>2.358928096152098</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -24527,28 +24527,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>12.15783415264313</v>
+        <v>13.12012939738015</v>
       </c>
       <c r="S27" t="n">
-        <v>84.68317110383782</v>
+        <v>84.64546634857484</v>
       </c>
       <c r="T27" t="n">
-        <v>113.1647286948216</v>
+        <v>113.1270239395586</v>
       </c>
       <c r="U27" t="n">
-        <v>138.9413820809748</v>
+        <v>138.9036773257118</v>
       </c>
       <c r="V27" t="n">
-        <v>145.8005871494253</v>
+        <v>145.7628823941623</v>
       </c>
       <c r="W27" t="n">
-        <v>164.6949831609196</v>
+        <v>164.6572784056566</v>
       </c>
       <c r="X27" t="n">
-        <v>118.7729852034775</v>
+        <v>118.7352804482145</v>
       </c>
       <c r="Y27" t="n">
-        <v>118.6826957773044</v>
+        <v>118.6449910220414</v>
       </c>
     </row>
     <row r="28">
@@ -24558,31 +24558,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>92.8319801819373</v>
+        <v>92.79427542667432</v>
       </c>
       <c r="C28" t="n">
-        <v>80.24682109862783</v>
+        <v>80.20911634336485</v>
       </c>
       <c r="D28" t="n">
-        <v>61.61547301821236</v>
+        <v>61.57776826294938</v>
       </c>
       <c r="E28" t="n">
-        <v>59.43396264656917</v>
+        <v>59.39625789130619</v>
       </c>
       <c r="F28" t="n">
-        <v>58.42104802293125</v>
+        <v>58.38334326766827</v>
       </c>
       <c r="G28" t="n">
-        <v>80.99097935845876</v>
+        <v>80.95327460319578</v>
       </c>
       <c r="H28" t="n">
-        <v>75.22717250743958</v>
+        <v>75.1894677521766</v>
       </c>
       <c r="I28" t="n">
-        <v>68.45047492725828</v>
+        <v>68.41277017199531</v>
       </c>
       <c r="J28" t="n">
-        <v>6.359180116672775</v>
+        <v>6.321475361409796</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -24606,28 +24606,28 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>90.29339137716948</v>
+        <v>90.25568662190651</v>
       </c>
       <c r="S28" t="n">
-        <v>137.0165980369723</v>
+        <v>136.9788932817093</v>
       </c>
       <c r="T28" t="n">
-        <v>140.9455894282815</v>
+        <v>140.9078846730185</v>
       </c>
       <c r="U28" t="n">
-        <v>198.4382293564909</v>
+        <v>199.2813246012279</v>
       </c>
       <c r="V28" t="n">
-        <v>165.137643323828</v>
+        <v>165.099938568565</v>
       </c>
       <c r="W28" t="n">
-        <v>198.522998336591</v>
+        <v>199.485293581328</v>
       </c>
       <c r="X28" t="n">
-        <v>137.7096553890372</v>
+        <v>138.6719506337742</v>
       </c>
       <c r="Y28" t="n">
-        <v>130.5846533520948</v>
+        <v>131.5469485968318</v>
       </c>
     </row>
     <row r="29">
@@ -24637,28 +24637,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>237.7338416634806</v>
+        <v>237.6646292700967</v>
       </c>
       <c r="C29" t="n">
-        <v>220.2728917710076</v>
+        <v>220.2036793776237</v>
       </c>
       <c r="D29" t="n">
-        <v>209.683041620683</v>
+        <v>209.6138292272991</v>
       </c>
       <c r="E29" t="n">
-        <v>236.9303700722618</v>
+        <v>236.8611576788779</v>
       </c>
       <c r="F29" t="n">
-        <v>261.8760457417114</v>
+        <v>261.8068333483276</v>
       </c>
       <c r="G29" t="n">
-        <v>269.302737515135</v>
+        <v>270.2335251217512</v>
       </c>
       <c r="H29" t="n">
-        <v>194.4748021157671</v>
+        <v>194.4055897223833</v>
       </c>
       <c r="I29" t="n">
-        <v>65.47588957040591</v>
+        <v>65.40667717702203</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -24685,28 +24685,28 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4.869117941149682</v>
+        <v>4.799905547765803</v>
       </c>
       <c r="S29" t="n">
-        <v>64.02006958624534</v>
+        <v>63.95085719286146</v>
       </c>
       <c r="T29" t="n">
-        <v>78.09584956413136</v>
+        <v>78.02663717074748</v>
       </c>
       <c r="U29" t="n">
-        <v>106.3456529078365</v>
+        <v>106.2764405144526</v>
       </c>
       <c r="V29" t="n">
-        <v>181.8714584701349</v>
+        <v>182.683046076751</v>
       </c>
       <c r="W29" t="n">
-        <v>203.240968717413</v>
+        <v>204.1717563240291</v>
       </c>
       <c r="X29" t="n">
-        <v>223.731100678469</v>
+        <v>224.6618882850852</v>
       </c>
       <c r="Y29" t="n">
-        <v>241.2379386560536</v>
+        <v>241.1687262626697</v>
       </c>
     </row>
     <row r="30">
@@ -24716,16 +24716,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>21.53318364986734</v>
+        <v>21.46397125648346</v>
       </c>
       <c r="C30" t="n">
-        <v>27.70849898831574</v>
+        <v>27.63928659493186</v>
       </c>
       <c r="D30" t="n">
-        <v>2.445065564638753</v>
+        <v>2.375853171254874</v>
       </c>
       <c r="E30" t="n">
-        <v>11.83349284878482</v>
+        <v>12.57586806201707</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -24767,25 +24767,25 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>26.68317110383782</v>
+        <v>26.61395871045394</v>
       </c>
       <c r="T30" t="n">
-        <v>54.1647286948216</v>
+        <v>55.09551630143773</v>
       </c>
       <c r="U30" t="n">
-        <v>80.94138208097482</v>
+        <v>80.87216968759094</v>
       </c>
       <c r="V30" t="n">
-        <v>87.80058714942527</v>
+        <v>87.73137475604139</v>
       </c>
       <c r="W30" t="n">
-        <v>105.6949831609196</v>
+        <v>106.6257707675357</v>
       </c>
       <c r="X30" t="n">
-        <v>60.77298520347748</v>
+        <v>60.7037728100936</v>
       </c>
       <c r="Y30" t="n">
-        <v>59.68269577730436</v>
+        <v>60.61348338392048</v>
       </c>
     </row>
     <row r="31">
@@ -24795,28 +24795,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>34.8319801819373</v>
+        <v>34.76276778855342</v>
       </c>
       <c r="C31" t="n">
-        <v>22.24682109862783</v>
+        <v>22.17760870524396</v>
       </c>
       <c r="D31" t="n">
-        <v>3.615473018212356</v>
+        <v>3.546260624828477</v>
       </c>
       <c r="E31" t="n">
-        <v>1.433962646569171</v>
+        <v>1.364750253185292</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4210480229312452</v>
+        <v>0.3518356295473666</v>
       </c>
       <c r="G31" t="n">
-        <v>22.99097935845876</v>
+        <v>22.92176696507488</v>
       </c>
       <c r="H31" t="n">
-        <v>17.22717250743958</v>
+        <v>17.1579601140557</v>
       </c>
       <c r="I31" t="n">
-        <v>10.45047492725828</v>
+        <v>10.38126253387441</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -24843,28 +24843,28 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>32.29339137716948</v>
+        <v>32.22417898378561</v>
       </c>
       <c r="S31" t="n">
-        <v>79.01659803697225</v>
+        <v>78.94738564358838</v>
       </c>
       <c r="T31" t="n">
-        <v>82.94558942828149</v>
+        <v>82.87637703489762</v>
       </c>
       <c r="U31" t="n">
-        <v>140.3190293564909</v>
+        <v>141.249816963107</v>
       </c>
       <c r="V31" t="n">
-        <v>106.137643323828</v>
+        <v>107.0684309304441</v>
       </c>
       <c r="W31" t="n">
-        <v>140.522998336591</v>
+        <v>141.4537859432071</v>
       </c>
       <c r="X31" t="n">
-        <v>79.82885538903716</v>
+        <v>80.64044299565327</v>
       </c>
       <c r="Y31" t="n">
-        <v>73.58465335209479</v>
+        <v>73.51544095871091</v>
       </c>
     </row>
     <row r="32">
@@ -24874,28 +24874,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>236.7338416634806</v>
+        <v>237.6646292700967</v>
       </c>
       <c r="C32" t="n">
-        <v>220.2728917710076</v>
+        <v>220.2036793776237</v>
       </c>
       <c r="D32" t="n">
-        <v>209.683041620683</v>
+        <v>209.6138292272991</v>
       </c>
       <c r="E32" t="n">
-        <v>236.9303700722618</v>
+        <v>236.8611576788779</v>
       </c>
       <c r="F32" t="n">
-        <v>261.8760457417114</v>
+        <v>261.8068333483276</v>
       </c>
       <c r="G32" t="n">
-        <v>270.302737515135</v>
+        <v>270.2335251217512</v>
       </c>
       <c r="H32" t="n">
-        <v>194.4748021157671</v>
+        <v>194.4055897223833</v>
       </c>
       <c r="I32" t="n">
-        <v>65.47588957040591</v>
+        <v>65.40667717702203</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -24922,28 +24922,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>4.869117941149682</v>
+        <v>4.799905547765803</v>
       </c>
       <c r="S32" t="n">
-        <v>64.02006958624534</v>
+        <v>63.95085719286146</v>
       </c>
       <c r="T32" t="n">
-        <v>77.09584956413136</v>
+        <v>78.02663717074748</v>
       </c>
       <c r="U32" t="n">
-        <v>106.3456529078365</v>
+        <v>106.2764405144526</v>
       </c>
       <c r="V32" t="n">
-        <v>182.7522584701349</v>
+        <v>182.683046076751</v>
       </c>
       <c r="W32" t="n">
-        <v>203.360168717413</v>
+        <v>204.1717563240291</v>
       </c>
       <c r="X32" t="n">
-        <v>224.731100678469</v>
+        <v>224.6618882850852</v>
       </c>
       <c r="Y32" t="n">
-        <v>240.2379386560536</v>
+        <v>241.1687262626697</v>
       </c>
     </row>
     <row r="33">
@@ -24953,16 +24953,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>21.53318364986734</v>
+        <v>21.46397125648346</v>
       </c>
       <c r="C33" t="n">
-        <v>27.70849898831574</v>
+        <v>27.63928659493186</v>
       </c>
       <c r="D33" t="n">
-        <v>2.445065564638753</v>
+        <v>2.375853171254874</v>
       </c>
       <c r="E33" t="n">
-        <v>12.64508045540094</v>
+        <v>12.57586806201707</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -25004,25 +25004,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>25.68317110383782</v>
+        <v>26.61395871045394</v>
       </c>
       <c r="T33" t="n">
-        <v>54.35314108820549</v>
+        <v>55.09551630143773</v>
       </c>
       <c r="U33" t="n">
-        <v>79.94138208097482</v>
+        <v>80.87216968759094</v>
       </c>
       <c r="V33" t="n">
-        <v>87.80058714942527</v>
+        <v>87.73137475604139</v>
       </c>
       <c r="W33" t="n">
-        <v>105.6949831609196</v>
+        <v>106.6257707675357</v>
       </c>
       <c r="X33" t="n">
-        <v>60.77298520347748</v>
+        <v>60.7037728100936</v>
       </c>
       <c r="Y33" t="n">
-        <v>60.68269577730436</v>
+        <v>60.61348338392048</v>
       </c>
     </row>
     <row r="34">
@@ -25032,28 +25032,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>34.8319801819373</v>
+        <v>34.76276778855342</v>
       </c>
       <c r="C34" t="n">
-        <v>22.24682109862783</v>
+        <v>22.17760870524396</v>
       </c>
       <c r="D34" t="n">
-        <v>2.615473018212356</v>
+        <v>3.546260624828477</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4339626465691708</v>
+        <v>1.364750253185292</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4210480229312452</v>
+        <v>0.3518356295473666</v>
       </c>
       <c r="G34" t="n">
-        <v>22.99097935845876</v>
+        <v>22.92176696507488</v>
       </c>
       <c r="H34" t="n">
-        <v>16.34637250743958</v>
+        <v>17.1579601140557</v>
       </c>
       <c r="I34" t="n">
-        <v>10.45047492725828</v>
+        <v>10.38126253387441</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -25080,28 +25080,28 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>32.29339137716948</v>
+        <v>32.22417898378561</v>
       </c>
       <c r="S34" t="n">
-        <v>79.01659803697225</v>
+        <v>78.94738564358838</v>
       </c>
       <c r="T34" t="n">
-        <v>82.94558942828149</v>
+        <v>82.87637703489762</v>
       </c>
       <c r="U34" t="n">
-        <v>140.3190293564909</v>
+        <v>141.249816963107</v>
       </c>
       <c r="V34" t="n">
-        <v>107.137643323828</v>
+        <v>107.0684309304441</v>
       </c>
       <c r="W34" t="n">
-        <v>141.522998336591</v>
+        <v>141.4537859432071</v>
       </c>
       <c r="X34" t="n">
-        <v>80.70965538903715</v>
+        <v>80.64044299565327</v>
       </c>
       <c r="Y34" t="n">
-        <v>73.58465335209479</v>
+        <v>73.51544095871091</v>
       </c>
     </row>
     <row r="35">
@@ -25111,28 +25111,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>237.7338416634806</v>
+        <v>237.6646292700967</v>
       </c>
       <c r="C35" t="n">
-        <v>220.2728917710076</v>
+        <v>220.2036793776237</v>
       </c>
       <c r="D35" t="n">
-        <v>209.683041620683</v>
+        <v>209.6138292272991</v>
       </c>
       <c r="E35" t="n">
-        <v>236.9303700722618</v>
+        <v>236.8611576788779</v>
       </c>
       <c r="F35" t="n">
-        <v>260.8760457417114</v>
+        <v>261.8068333483276</v>
       </c>
       <c r="G35" t="n">
-        <v>269.302737515135</v>
+        <v>270.2335251217512</v>
       </c>
       <c r="H35" t="n">
-        <v>193.5940021157671</v>
+        <v>194.4055897223833</v>
       </c>
       <c r="I35" t="n">
-        <v>65.47588957040591</v>
+        <v>65.40667717702203</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -25159,28 +25159,28 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4.869117941149682</v>
+        <v>4.799905547765803</v>
       </c>
       <c r="S35" t="n">
-        <v>64.02006958624534</v>
+        <v>63.95085719286146</v>
       </c>
       <c r="T35" t="n">
-        <v>78.09584956413136</v>
+        <v>78.02663717074748</v>
       </c>
       <c r="U35" t="n">
-        <v>106.3456529078365</v>
+        <v>106.2764405144526</v>
       </c>
       <c r="V35" t="n">
-        <v>182.7522584701349</v>
+        <v>182.683046076751</v>
       </c>
       <c r="W35" t="n">
-        <v>204.240968717413</v>
+        <v>204.1717563240291</v>
       </c>
       <c r="X35" t="n">
-        <v>223.731100678469</v>
+        <v>224.6618882850852</v>
       </c>
       <c r="Y35" t="n">
-        <v>241.2379386560536</v>
+        <v>241.1687262626697</v>
       </c>
     </row>
     <row r="36">
@@ -25190,19 +25190,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>20.65238364986735</v>
+        <v>21.46397125648346</v>
       </c>
       <c r="C36" t="n">
-        <v>27.70849898831574</v>
+        <v>27.63928659493186</v>
       </c>
       <c r="D36" t="n">
-        <v>2.445065564638753</v>
+        <v>2.375853171254874</v>
       </c>
       <c r="E36" t="n">
-        <v>12.64508045540094</v>
+        <v>12.57586806201707</v>
       </c>
       <c r="F36" t="n">
-        <v>0.06921239338387863</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -25241,25 +25241,25 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>26.68317110383782</v>
+        <v>26.61395871045394</v>
       </c>
       <c r="T36" t="n">
-        <v>54.1647286948216</v>
+        <v>55.09551630143773</v>
       </c>
       <c r="U36" t="n">
-        <v>79.94138208097482</v>
+        <v>80.87216968759094</v>
       </c>
       <c r="V36" t="n">
-        <v>87.80058714942527</v>
+        <v>87.73137475604139</v>
       </c>
       <c r="W36" t="n">
-        <v>106.6949831609196</v>
+        <v>106.6257707675357</v>
       </c>
       <c r="X36" t="n">
-        <v>60.77298520347748</v>
+        <v>60.7037728100936</v>
       </c>
       <c r="Y36" t="n">
-        <v>59.68269577730436</v>
+        <v>60.61348338392048</v>
       </c>
     </row>
     <row r="37">
@@ -25269,28 +25269,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>34.8319801819373</v>
+        <v>34.76276778855342</v>
       </c>
       <c r="C37" t="n">
-        <v>22.24682109862783</v>
+        <v>22.17760870524396</v>
       </c>
       <c r="D37" t="n">
-        <v>3.615473018212356</v>
+        <v>3.546260624828477</v>
       </c>
       <c r="E37" t="n">
-        <v>1.433962646569171</v>
+        <v>1.364750253185292</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4210480229312452</v>
+        <v>0.3518356295473666</v>
       </c>
       <c r="G37" t="n">
-        <v>22.99097935845876</v>
+        <v>22.92176696507488</v>
       </c>
       <c r="H37" t="n">
-        <v>17.22717250743958</v>
+        <v>17.1579601140557</v>
       </c>
       <c r="I37" t="n">
-        <v>10.45047492725828</v>
+        <v>10.38126253387441</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -25317,28 +25317,28 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>31.29339137716948</v>
+        <v>32.22417898378561</v>
       </c>
       <c r="S37" t="n">
-        <v>78.01659803697225</v>
+        <v>78.94738564358838</v>
       </c>
       <c r="T37" t="n">
-        <v>82.94558942828149</v>
+        <v>82.87637703489762</v>
       </c>
       <c r="U37" t="n">
-        <v>141.3190293564909</v>
+        <v>141.249816963107</v>
       </c>
       <c r="V37" t="n">
-        <v>106.137643323828</v>
+        <v>107.0684309304441</v>
       </c>
       <c r="W37" t="n">
-        <v>140.642198336591</v>
+        <v>141.4537859432071</v>
       </c>
       <c r="X37" t="n">
-        <v>80.70965538903715</v>
+        <v>80.64044299565327</v>
       </c>
       <c r="Y37" t="n">
-        <v>73.58465335209479</v>
+        <v>73.51544095871091</v>
       </c>
     </row>
     <row r="38">
@@ -25348,28 +25348,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>236.8530416634806</v>
+        <v>237.6646292700967</v>
       </c>
       <c r="C38" t="n">
-        <v>220.2728917710076</v>
+        <v>220.2036793776237</v>
       </c>
       <c r="D38" t="n">
-        <v>209.683041620683</v>
+        <v>209.6138292272991</v>
       </c>
       <c r="E38" t="n">
-        <v>236.9303700722618</v>
+        <v>236.8611576788779</v>
       </c>
       <c r="F38" t="n">
-        <v>260.8760457417114</v>
+        <v>261.8068333483276</v>
       </c>
       <c r="G38" t="n">
-        <v>269.302737515135</v>
+        <v>270.2335251217512</v>
       </c>
       <c r="H38" t="n">
-        <v>193.4748021157671</v>
+        <v>194.4055897223833</v>
       </c>
       <c r="I38" t="n">
-        <v>65.47588957040591</v>
+        <v>65.40667717702203</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -25396,28 +25396,28 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.869117941149682</v>
+        <v>4.799905547765803</v>
       </c>
       <c r="S38" t="n">
-        <v>64.02006958624534</v>
+        <v>63.95085719286146</v>
       </c>
       <c r="T38" t="n">
-        <v>78.09584956413136</v>
+        <v>78.02663717074748</v>
       </c>
       <c r="U38" t="n">
-        <v>106.3456529078365</v>
+        <v>106.2764405144526</v>
       </c>
       <c r="V38" t="n">
-        <v>182.7522584701349</v>
+        <v>182.683046076751</v>
       </c>
       <c r="W38" t="n">
-        <v>204.240968717413</v>
+        <v>204.1717563240291</v>
       </c>
       <c r="X38" t="n">
-        <v>224.731100678469</v>
+        <v>224.6618882850852</v>
       </c>
       <c r="Y38" t="n">
-        <v>241.2379386560536</v>
+        <v>241.1687262626697</v>
       </c>
     </row>
     <row r="39">
@@ -25427,16 +25427,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>21.53318364986734</v>
+        <v>21.46397125648346</v>
       </c>
       <c r="C39" t="n">
-        <v>26.89691138169962</v>
+        <v>27.63928659493186</v>
       </c>
       <c r="D39" t="n">
-        <v>2.445065564638753</v>
+        <v>2.375853171254874</v>
       </c>
       <c r="E39" t="n">
-        <v>12.64508045540094</v>
+        <v>12.57586806201707</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -25478,25 +25478,25 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>26.68317110383782</v>
+        <v>26.61395871045394</v>
       </c>
       <c r="T39" t="n">
-        <v>54.1647286948216</v>
+        <v>55.09551630143773</v>
       </c>
       <c r="U39" t="n">
-        <v>80.94138208097482</v>
+        <v>80.87216968759094</v>
       </c>
       <c r="V39" t="n">
-        <v>86.80058714942527</v>
+        <v>87.73137475604139</v>
       </c>
       <c r="W39" t="n">
-        <v>105.6949831609196</v>
+        <v>106.6257707675357</v>
       </c>
       <c r="X39" t="n">
-        <v>60.77298520347748</v>
+        <v>60.7037728100936</v>
       </c>
       <c r="Y39" t="n">
-        <v>60.68269577730436</v>
+        <v>60.61348338392048</v>
       </c>
     </row>
     <row r="40">
@@ -25506,28 +25506,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>34.8319801819373</v>
+        <v>34.76276778855342</v>
       </c>
       <c r="C40" t="n">
-        <v>22.24682109862783</v>
+        <v>22.17760870524396</v>
       </c>
       <c r="D40" t="n">
-        <v>3.615473018212356</v>
+        <v>3.546260624828477</v>
       </c>
       <c r="E40" t="n">
-        <v>1.433962646569171</v>
+        <v>1.364750253185292</v>
       </c>
       <c r="F40" t="n">
-        <v>0.4210480229312452</v>
+        <v>0.3518356295473666</v>
       </c>
       <c r="G40" t="n">
-        <v>22.99097935845876</v>
+        <v>22.92176696507488</v>
       </c>
       <c r="H40" t="n">
-        <v>17.22717250743958</v>
+        <v>17.1579601140557</v>
       </c>
       <c r="I40" t="n">
-        <v>10.45047492725828</v>
+        <v>10.38126253387441</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -25554,28 +25554,28 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>32.29339137716948</v>
+        <v>32.22417898378561</v>
       </c>
       <c r="S40" t="n">
-        <v>79.01659803697225</v>
+        <v>78.94738564358838</v>
       </c>
       <c r="T40" t="n">
-        <v>82.0647894282815</v>
+        <v>82.87637703489762</v>
       </c>
       <c r="U40" t="n">
-        <v>141.3190293564909</v>
+        <v>141.249816963107</v>
       </c>
       <c r="V40" t="n">
-        <v>106.137643323828</v>
+        <v>107.0684309304441</v>
       </c>
       <c r="W40" t="n">
-        <v>141.522998336591</v>
+        <v>141.4537859432071</v>
       </c>
       <c r="X40" t="n">
-        <v>79.70965538903715</v>
+        <v>80.64044299565327</v>
       </c>
       <c r="Y40" t="n">
-        <v>72.58465335209479</v>
+        <v>73.51544095871091</v>
       </c>
     </row>
     <row r="41">
@@ -25585,28 +25585,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>244.7338416634806</v>
+        <v>245.3903245002699</v>
       </c>
       <c r="C41" t="n">
-        <v>228.2728917710076</v>
+        <v>227.9293746077969</v>
       </c>
       <c r="D41" t="n">
-        <v>217.683041620683</v>
+        <v>217.3395244574723</v>
       </c>
       <c r="E41" t="n">
-        <v>244.9303700722618</v>
+        <v>244.5868529090511</v>
       </c>
       <c r="F41" t="n">
-        <v>269.8760457417114</v>
+        <v>269.5325285785008</v>
       </c>
       <c r="G41" t="n">
-        <v>277.421937515135</v>
+        <v>277.9592203519244</v>
       </c>
       <c r="H41" t="n">
-        <v>201.4748021157671</v>
+        <v>202.1312849525565</v>
       </c>
       <c r="I41" t="n">
-        <v>73.47588957040591</v>
+        <v>73.13237240719528</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25633,28 +25633,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>11.86911794114968</v>
+        <v>12.52560077793905</v>
       </c>
       <c r="S41" t="n">
-        <v>72.02006958624534</v>
+        <v>71.67655242303471</v>
       </c>
       <c r="T41" t="n">
-        <v>86.09584956413136</v>
+        <v>85.75233240092072</v>
       </c>
       <c r="U41" t="n">
-        <v>114.3456529078365</v>
+        <v>114.0021357446259</v>
       </c>
       <c r="V41" t="n">
-        <v>190.7522584701349</v>
+        <v>190.4087413069243</v>
       </c>
       <c r="W41" t="n">
-        <v>212.240968717413</v>
+        <v>211.8974515542024</v>
       </c>
       <c r="X41" t="n">
-        <v>232.731100678469</v>
+        <v>232.3875835152584</v>
       </c>
       <c r="Y41" t="n">
-        <v>249.2379386560536</v>
+        <v>248.894421492843</v>
       </c>
     </row>
     <row r="42">
@@ -25664,19 +25664,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29.53318364986734</v>
+        <v>29.18966648665671</v>
       </c>
       <c r="C42" t="n">
-        <v>35.70849898831574</v>
+        <v>35.3649818251051</v>
       </c>
       <c r="D42" t="n">
-        <v>9.445065564638753</v>
+        <v>10.10154840142812</v>
       </c>
       <c r="E42" t="n">
-        <v>19.64508045540094</v>
+        <v>20.30156329219031</v>
       </c>
       <c r="F42" t="n">
-        <v>7.531929556594513</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -25715,25 +25715,25 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>33.68317110383782</v>
+        <v>34.33965394062719</v>
       </c>
       <c r="T42" t="n">
-        <v>63.1647286948216</v>
+        <v>62.82121153161097</v>
       </c>
       <c r="U42" t="n">
-        <v>88.94138208097482</v>
+        <v>88.59786491776418</v>
       </c>
       <c r="V42" t="n">
-        <v>95.80058714942527</v>
+        <v>95.45706998621463</v>
       </c>
       <c r="W42" t="n">
-        <v>114.6949831609196</v>
+        <v>114.351465997709</v>
       </c>
       <c r="X42" t="n">
-        <v>68.77298520347748</v>
+        <v>68.42946804026684</v>
       </c>
       <c r="Y42" t="n">
-        <v>68.68269577730436</v>
+        <v>68.33917861409373</v>
       </c>
     </row>
     <row r="43">
@@ -25743,28 +25743,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>42.8319801819373</v>
+        <v>42.48846301872666</v>
       </c>
       <c r="C43" t="n">
-        <v>29.24682109862783</v>
+        <v>29.9033039354172</v>
       </c>
       <c r="D43" t="n">
-        <v>11.61547301821236</v>
+        <v>11.27195585500172</v>
       </c>
       <c r="E43" t="n">
-        <v>9.433962646569171</v>
+        <v>9.090445483358536</v>
       </c>
       <c r="F43" t="n">
-        <v>8.421048022931245</v>
+        <v>8.077530859720611</v>
       </c>
       <c r="G43" t="n">
-        <v>29.99097935845876</v>
+        <v>30.64746219524812</v>
       </c>
       <c r="H43" t="n">
-        <v>24.22717250743958</v>
+        <v>24.88365534422894</v>
       </c>
       <c r="I43" t="n">
-        <v>18.45047492725828</v>
+        <v>18.10695776404765</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25791,28 +25791,28 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>39.41259137716948</v>
+        <v>39.94987421395885</v>
       </c>
       <c r="S43" t="n">
-        <v>87.01659803697225</v>
+        <v>86.67308087376162</v>
       </c>
       <c r="T43" t="n">
-        <v>90.94558942828149</v>
+        <v>90.60207226507086</v>
       </c>
       <c r="U43" t="n">
-        <v>149.3190293564909</v>
+        <v>148.9755121932803</v>
       </c>
       <c r="V43" t="n">
-        <v>115.137643323828</v>
+        <v>114.7941261606174</v>
       </c>
       <c r="W43" t="n">
-        <v>149.522998336591</v>
+        <v>149.1794811733804</v>
       </c>
       <c r="X43" t="n">
-        <v>88.70965538903715</v>
+        <v>88.36613822582652</v>
       </c>
       <c r="Y43" t="n">
-        <v>81.58465335209479</v>
+        <v>81.24113618888416</v>
       </c>
     </row>
     <row r="44">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>328686.1893140328</v>
+        <v>328576.2892033489</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>498244.7259813184</v>
+        <v>498789.7536365564</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>498244.7259813184</v>
+        <v>498789.7536365564</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>499043.713606369</v>
+        <v>498789.7536365564</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>499043.713606369</v>
+        <v>498789.7536365564</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>490608.8980967589</v>
+        <v>489889.9953718869</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>607309.9880151668</v>
+        <v>606645.9479462404</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>607309.9880151668</v>
+        <v>606645.9479462404</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>607309.9880151668</v>
+        <v>606645.9479462404</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>607309.9880151668</v>
+        <v>606645.9479462404</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>591698.7994002186</v>
+        <v>591582.696414258</v>
       </c>
     </row>
     <row r="16">
@@ -26264,43 +26264,43 @@
         <v>696384.8879094827</v>
       </c>
       <c r="C2" t="n">
-        <v>696384.8879094826</v>
+        <v>696384.8879094829</v>
       </c>
       <c r="D2" t="n">
-        <v>696384.8879094827</v>
+        <v>696384.8879094828</v>
       </c>
       <c r="E2" t="n">
-        <v>208891.0735724426</v>
+        <v>208787.2790234635</v>
       </c>
       <c r="F2" t="n">
-        <v>369029.6915359901</v>
+        <v>369544.4398770484</v>
       </c>
       <c r="G2" t="n">
-        <v>369029.6915359901</v>
+        <v>369544.4398770478</v>
       </c>
       <c r="H2" t="n">
-        <v>369511.2988159905</v>
+        <v>369544.4398770484</v>
       </c>
       <c r="I2" t="n">
-        <v>369511.2988159905</v>
+        <v>369544.4398770483</v>
       </c>
       <c r="J2" t="n">
-        <v>361545.0841680248</v>
+        <v>361139.1126270826</v>
       </c>
       <c r="K2" t="n">
-        <v>471762.7802020771</v>
+        <v>471408.6233917498</v>
       </c>
       <c r="L2" t="n">
-        <v>471762.780202077</v>
+        <v>471408.6233917506</v>
       </c>
       <c r="M2" t="n">
-        <v>471762.780202077</v>
+        <v>471408.6233917504</v>
       </c>
       <c r="N2" t="n">
-        <v>471762.7802020769</v>
+        <v>471408.6233917503</v>
       </c>
       <c r="O2" t="n">
-        <v>457018.8798435149</v>
+        <v>457182.2191670993</v>
       </c>
       <c r="P2" t="n">
         <v>182762.5894034589</v>
@@ -26322,25 +26322,25 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>9600</v>
+        <v>9559.431483690014</v>
       </c>
       <c r="F3" t="n">
-        <v>63200</v>
+        <v>63449.60762007179</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>269.809</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>6400</v>
+        <v>6180.556184138595</v>
       </c>
       <c r="K3" t="n">
-        <v>109600</v>
+        <v>109874.8137305685</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>452399.9905489652</v>
+        <v>451872.6453349188</v>
       </c>
       <c r="C4" t="n">
-        <v>452399.9905489652</v>
+        <v>451872.6453349188</v>
       </c>
       <c r="D4" t="n">
-        <v>452399.9905489652</v>
+        <v>451872.6453349188</v>
       </c>
       <c r="E4" t="n">
-        <v>125052.4390586939</v>
+        <v>124455.3967726702</v>
       </c>
       <c r="F4" t="n">
-        <v>232584.0280711461</v>
+        <v>232402.3315691932</v>
       </c>
       <c r="G4" t="n">
-        <v>232584.0280711461</v>
+        <v>232402.3315691932</v>
       </c>
       <c r="H4" t="n">
-        <v>232873.9457277118</v>
+        <v>232402.3315691932</v>
       </c>
       <c r="I4" t="n">
-        <v>232873.9457277118</v>
+        <v>232402.3315691932</v>
       </c>
       <c r="J4" t="n">
-        <v>227524.7068595148</v>
+        <v>226758.2326825385</v>
       </c>
       <c r="K4" t="n">
-        <v>301534.8622021249</v>
+        <v>300803.1811336951</v>
       </c>
       <c r="L4" t="n">
-        <v>301534.8622021249</v>
+        <v>300803.1811336952</v>
       </c>
       <c r="M4" t="n">
-        <v>301534.862202125</v>
+        <v>300803.1811336951</v>
       </c>
       <c r="N4" t="n">
-        <v>301534.8622021249</v>
+        <v>300803.1811336952</v>
       </c>
       <c r="O4" t="n">
-        <v>291634.4705666835</v>
+        <v>291250.2833276311</v>
       </c>
       <c r="P4" t="n">
-        <v>107507.4055314464</v>
+        <v>106980.0603174001</v>
       </c>
     </row>
     <row r="5">
@@ -26426,37 +26426,37 @@
         <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1008.828</v>
+        <v>1004.56480675292</v>
       </c>
       <c r="F5" t="n">
-        <v>7650.279</v>
+        <v>7672.246135517689</v>
       </c>
       <c r="G5" t="n">
-        <v>7650.279</v>
+        <v>7672.246135517689</v>
       </c>
       <c r="H5" t="n">
-        <v>7711.079000000001</v>
+        <v>7672.246135517689</v>
       </c>
       <c r="I5" t="n">
-        <v>7711.079000000001</v>
+        <v>7672.246135517689</v>
       </c>
       <c r="J5" t="n">
-        <v>7374.803000000001</v>
+        <v>7317.172801070204</v>
       </c>
       <c r="K5" t="n">
-        <v>12250.805</v>
+        <v>12195.82361669939</v>
       </c>
       <c r="L5" t="n">
-        <v>12250.805</v>
+        <v>12195.82361669939</v>
       </c>
       <c r="M5" t="n">
-        <v>12250.805</v>
+        <v>12195.82361669939</v>
       </c>
       <c r="N5" t="n">
-        <v>12250.805</v>
+        <v>12195.82361669939</v>
       </c>
       <c r="O5" t="n">
-        <v>11578.253</v>
+        <v>11546.33214439395</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>210357.2973605175</v>
+        <v>210884.6425745639</v>
       </c>
       <c r="C6" t="n">
-        <v>210357.2973605174</v>
+        <v>210884.6425745641</v>
       </c>
       <c r="D6" t="n">
-        <v>210357.2973605175</v>
+        <v>210884.642574564</v>
       </c>
       <c r="E6" t="n">
-        <v>73229.80651374876</v>
+        <v>73767.88596035035</v>
       </c>
       <c r="F6" t="n">
-        <v>65595.384464844</v>
+        <v>66020.25455226577</v>
       </c>
       <c r="G6" t="n">
-        <v>128795.384464844</v>
+        <v>129469.862172337</v>
       </c>
       <c r="H6" t="n">
-        <v>128656.4650882787</v>
+        <v>129469.8621723376</v>
       </c>
       <c r="I6" t="n">
-        <v>128926.2740882787</v>
+        <v>129469.8621723375</v>
       </c>
       <c r="J6" t="n">
-        <v>120245.57430851</v>
+        <v>120883.1509593353</v>
       </c>
       <c r="K6" t="n">
-        <v>48377.11299995216</v>
+        <v>48534.80491078678</v>
       </c>
       <c r="L6" t="n">
-        <v>157977.1129999521</v>
+        <v>158409.618641356</v>
       </c>
       <c r="M6" t="n">
-        <v>157977.112999952</v>
+        <v>158409.6186413559</v>
       </c>
       <c r="N6" t="n">
-        <v>157977.112999952</v>
+        <v>158409.6186413557</v>
       </c>
       <c r="O6" t="n">
-        <v>153806.1562768314</v>
+        <v>154385.6036950742</v>
       </c>
       <c r="P6" t="n">
-        <v>75255.18387201249</v>
+        <v>75782.52908605884</v>
       </c>
     </row>
   </sheetData>
@@ -26632,37 +26632,37 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F2" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G2" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H2" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I2" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J2" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="K2" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="L2" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="M2" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="N2" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="O2" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -26745,28 +26745,28 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,7 +26840,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -26849,40 +26849,40 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F2" t="n">
-        <v>79</v>
+        <v>79.31200952508974</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>8</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="K2" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27081,10 +27081,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K2" t="n">
-        <v>79</v>
+        <v>79.31200952508974</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27096,10 +27096,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>7.725695230173244</v>
       </c>
       <c r="P2" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="3">
@@ -27203,7 +27203,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -28012,28 +28012,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -28060,28 +28060,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="T11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="U11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="V11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="W11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
     </row>
     <row r="12">
@@ -28091,28 +28091,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -28139,28 +28139,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="T12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="U12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="V12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="W12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="Y12" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
     </row>
     <row r="13">
@@ -28170,34 +28170,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="H13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="J13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -28215,31 +28215,31 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="R13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="T13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="V13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="W13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="X13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="Y13" t="n">
-        <v>12</v>
+        <v>11.94928935461252</v>
       </c>
     </row>
     <row r="14">
@@ -28249,28 +28249,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -28297,28 +28297,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y14" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="15">
@@ -28328,25 +28328,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C15" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D15" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E15" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F15" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G15" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H15" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I15" t="n">
         <v>89.39663285141508</v>
@@ -28376,28 +28376,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S15" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T15" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U15" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V15" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W15" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X15" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y15" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="16">
@@ -28407,31 +28407,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="K16" t="n">
         <v>22.26949182588285</v>
@@ -28455,28 +28455,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y16" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="17">
@@ -28486,28 +28486,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -28534,28 +28534,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y17" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="18">
@@ -28565,25 +28565,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C18" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D18" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E18" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F18" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G18" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H18" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I18" t="n">
         <v>89.39663285141508</v>
@@ -28613,28 +28613,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S18" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T18" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U18" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V18" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W18" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X18" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y18" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="19">
@@ -28644,31 +28644,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="K19" t="n">
         <v>22.26949182588285</v>
@@ -28692,28 +28692,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y19" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="20">
@@ -28723,28 +28723,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J20" t="n">
         <v>11.94928935461252</v>
@@ -28771,28 +28771,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y20" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="21">
@@ -28802,25 +28802,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D21" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E21" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F21" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G21" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H21" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I21" t="n">
         <v>89.39663285141508</v>
@@ -28850,28 +28850,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S21" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T21" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U21" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V21" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W21" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X21" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y21" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="22">
@@ -28881,31 +28881,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="K22" t="n">
         <v>22.26949182588285</v>
@@ -28929,28 +28929,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y22" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="23">
@@ -28960,28 +28960,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J23" t="n">
         <v>11.94928935461252</v>
@@ -29008,28 +29008,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y23" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="24">
@@ -29039,25 +29039,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C24" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D24" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E24" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F24" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G24" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H24" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I24" t="n">
         <v>89.39663285141508</v>
@@ -29087,28 +29087,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S24" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T24" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U24" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V24" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W24" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X24" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y24" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="25">
@@ -29118,31 +29118,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="C25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="D25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="E25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="F25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="G25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="H25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="I25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="J25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="K25" t="n">
         <v>22.26949182588285</v>
@@ -29166,28 +29166,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="S25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="T25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="U25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="V25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="W25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="X25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
       <c r="Y25" t="n">
-        <v>91</v>
+        <v>91.26129887970225</v>
       </c>
     </row>
     <row r="26">
@@ -29197,28 +29197,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="C26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="D26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="E26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="F26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="G26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="H26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="I26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="J26" t="n">
         <v>11.94928935461252</v>
@@ -29245,28 +29245,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="S26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="T26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="U26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="V26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="W26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="X26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="Y26" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
     </row>
     <row r="27">
@@ -29276,28 +29276,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="C27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="D27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="E27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="F27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="G27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="H27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="I27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="J27" t="n">
         <v>0.7465913262578567</v>
@@ -29324,28 +29324,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="S27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="T27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="U27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="V27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="W27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="X27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="Y27" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
     </row>
     <row r="28">
@@ -29355,31 +29355,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="C28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="D28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="E28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="F28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="G28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="H28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="I28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="J28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="K28" t="n">
         <v>22.26949182588285</v>
@@ -29403,28 +29403,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="S28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="T28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="U28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="V28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="W28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="X28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
       <c r="Y28" t="n">
-        <v>87</v>
+        <v>87.03770475526298</v>
       </c>
     </row>
     <row r="29">
@@ -29434,28 +29434,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J29" t="n">
         <v>11.94928935461252</v>
@@ -29482,28 +29482,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y29" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="30">
@@ -29513,19 +29513,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C30" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D30" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E30" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F30" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
         <v>137.3435171632106</v>
@@ -29564,25 +29564,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T30" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U30" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V30" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W30" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X30" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y30" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="31">
@@ -29592,28 +29592,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J31" t="n">
         <v>93.35918011667277</v>
@@ -29640,28 +29640,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y31" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="32">
@@ -29671,28 +29671,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J32" t="n">
         <v>11.94928935461252</v>
@@ -29719,28 +29719,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y32" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="33">
@@ -29750,19 +29750,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C33" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D33" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E33" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F33" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
         <v>137.3435171632106</v>
@@ -29801,25 +29801,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T33" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U33" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V33" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W33" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X33" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y33" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="34">
@@ -29829,28 +29829,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J34" t="n">
         <v>93.35918011667277</v>
@@ -29877,28 +29877,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y34" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="35">
@@ -29908,28 +29908,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J35" t="n">
         <v>11.94928935461252</v>
@@ -29956,28 +29956,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y35" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="36">
@@ -29987,19 +29987,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C36" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D36" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E36" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F36" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
         <v>137.3435171632106</v>
@@ -30038,25 +30038,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T36" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U36" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V36" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W36" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X36" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y36" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="37">
@@ -30066,28 +30066,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J37" t="n">
         <v>93.35918011667277</v>
@@ -30114,28 +30114,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y37" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="38">
@@ -30145,28 +30145,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J38" t="n">
         <v>11.94928935461252</v>
@@ -30193,28 +30193,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y38" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="39">
@@ -30224,19 +30224,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C39" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D39" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E39" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F39" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
         <v>137.3435171632106</v>
@@ -30275,25 +30275,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T39" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U39" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V39" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W39" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X39" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y39" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="40">
@@ -30303,28 +30303,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="C40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="D40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="E40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="F40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="H40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="I40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="J40" t="n">
         <v>93.35918011667277</v>
@@ -30351,28 +30351,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="S40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="T40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="U40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="V40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="W40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="X40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="Y40" t="n">
-        <v>145</v>
+        <v>145.0692123933839</v>
       </c>
     </row>
     <row r="41">
@@ -30382,28 +30382,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -30430,28 +30430,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y41" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="42">
@@ -30461,22 +30461,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C42" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D42" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E42" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F42" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G42" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
         <v>112.2354442364965</v>
@@ -30512,25 +30512,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T42" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U42" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V42" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W42" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X42" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y42" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="43">
@@ -30540,28 +30540,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="C43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="D43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="E43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="F43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="G43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="I43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="J43" t="n">
         <v>93.35918011667277</v>
@@ -30588,28 +30588,28 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="S43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="T43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="U43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="V43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="W43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="X43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="Y43" t="n">
-        <v>137</v>
+        <v>137.3435171632106</v>
       </c>
     </row>
     <row r="44">
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9595959595959592</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -36045,13 +36045,13 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36115,7 +36115,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9595959595959592</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -36124,13 +36124,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -36197,16 +36197,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.9595959595959592</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -36276,16 +36276,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9595959595959592</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -36355,16 +36355,16 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9595959595959591</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -36434,16 +36434,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.9595959595959592</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -36510,16 +36510,16 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0.9595959595959598</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -36595,16 +36595,16 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.9595959595959598</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36671,16 +36671,16 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.9595959595959592</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -36750,19 +36750,19 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.9595959595959592</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36829,22 +36829,22 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9595959595959591</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36908,16 +36908,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.9595959595959592</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -36987,19 +36987,19 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9595959595959592</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37063,16 +37063,16 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.9595959595959591</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -37145,16 +37145,16 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.9595959595959592</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -37221,16 +37221,16 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0.9595959595959598</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -37300,7 +37300,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -37309,13 +37309,13 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.9595959595959598</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37382,16 +37382,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.9595959595959592</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -37464,16 +37464,16 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.9595959595959598</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37540,19 +37540,19 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.9595959595959592</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37619,16 +37619,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.9595959595959592</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -37695,16 +37695,16 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0.9595959595959598</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -37777,19 +37777,19 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.9595959595959592</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37856,16 +37856,16 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.9595959595959592</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
